--- a/data/trans_orig/IP19C06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Habitat-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79257</t>
+          <t>79564</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154614</t>
+          <t>154898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>87212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182334</t>
+          <t>182528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357895</t>
+          <t>357730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707436</t>
+          <t>708139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109987</t>
+          <t>110238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>223455</t>
+          <t>224362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70404</t>
+          <t>70809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74750</t>
+          <t>75501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148835</t>
+          <t>148749</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153823</t>
+          <t>153815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87455</t>
+          <t>87474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92013</t>
+          <t>92195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182525</t>
+          <t>183083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188528</t>
+          <t>188575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>346655</t>
+          <t>346712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>352864</t>
+          <t>352863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>359882</t>
+          <t>359796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365984</t>
+          <t>365380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,99%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709607</t>
+          <t>709681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>717488</t>
+          <t>717473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66986</t>
+          <t>66916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142581</t>
+          <t>142825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104122</t>
+          <t>104045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212406</t>
+          <t>212724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72946</t>
+          <t>73005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148236</t>
+          <t>148945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357974</t>
+          <t>357644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364488</t>
+          <t>364495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>724482</t>
+          <t>724651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730007</t>
+          <t>730014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65499</t>
+          <t>65851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150859</t>
+          <t>150499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108904</t>
+          <t>109047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113342</t>
+          <t>113733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159407</t>
+          <t>160756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>272624</t>
+          <t>272687</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280070</t>
+          <t>280060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104628</t>
+          <t>104735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115631</t>
+          <t>114754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220624</t>
+          <t>221944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94538</t>
+          <t>94138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100456</t>
+          <t>100380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205931</t>
+          <t>206023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211967</t>
+          <t>211964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381139</t>
+          <t>380540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>388976</t>
+          <t>388868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>475886</t>
+          <t>475881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>860680</t>
+          <t>860933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871797</t>
+          <t>871994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2659</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2963</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81663</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79529</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>81663</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79564</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154898</t>
+          <t>155216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4008</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3504</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>89348</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>87209</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>89348</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>87212</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182528</t>
+          <t>182024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,107 +2095,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4350</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4001</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4387</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4522</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>360512</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>357381</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>360512</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>357730</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>708139</t>
+          <t>708274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>73918</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,107 +3013,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2361</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3295</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2944</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>112017</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>110238</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>109304</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>337</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224362</t>
+          <t>224382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4609</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1128</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3688</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3697</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4252</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78896</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75144</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>73369</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70809</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70800</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,49%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,04%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78896</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75501</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>235</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148749</t>
+          <t>148531</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153815</t>
+          <t>153819</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,67 +3704,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4602</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1519</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5503</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5245</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4106</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>94936</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>91699</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>91458</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>87474</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>87732</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>94936</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>92195</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>247</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183083</t>
+          <t>182266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188575</t>
+          <t>188571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6517</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1128</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7279</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7087</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6206</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4155,74 +4155,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>363779</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>359485</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>365386</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>350761</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>346712</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>352863</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>346904</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>352849</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>363779</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>359796</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>365380</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1020</t>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709681</t>
+          <t>710078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>717473</t>
+          <t>717580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,107 +4617,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3925</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4965</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3866</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3812</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4735,69 +4735,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>70070</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66916</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>65876</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,91%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>194</t>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142825</t>
+          <t>142771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,107 +4960,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3672</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3050</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>106566</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>104045</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>103511</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>322</t>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212724</t>
+          <t>212351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,92 +5303,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3858</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76163</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73276</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76163</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>73005</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148945</t>
+          <t>148943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5759,47 +5759,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>109007</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,107 +5989,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4974</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5975</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -6102,107 +6102,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>367308</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>364505</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>361230</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>357644</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>357200</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>367308</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>364495</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>728538</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>725070</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>730626</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>728538</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>724651</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>730014</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3915</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4521</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4039</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4516</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>69021</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65851</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>73475</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69757</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>74278</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85249</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>202</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>154270</t>
+          <t>154932</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150499</t>
+          <t>151696</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1730</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4686</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>161689</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>159091</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>112003</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>109047</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>166044</t>
+          <t>115325</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160756</t>
+          <t>112347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>278047</t>
+          <t>277015</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>272687</t>
+          <t>273917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280060</t>
+          <t>278676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>964</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>366</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>111134</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>106994</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>106533</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>104735</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>102073</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>100659</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>102439</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>119202</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>114754</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>120247</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>268</t>
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>225735</t>
+          <t>213206</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221944</t>
+          <t>209177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7041</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>770</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>98318</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>94138</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>100380</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>99716</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>209889</t>
+          <t>204925</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206023</t>
+          <t>200839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211964</t>
+          <t>207014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2765</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11093</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>459490</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>455261</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>545</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>385875</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>380540</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>388868</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>482067</t>
+          <t>390589</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>475881</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>393489</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>867941</t>
+          <t>850078</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>860933</t>
+          <t>844844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871994</t>
+          <t>853785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
